--- a/Result/profitability/1308.xlsx
+++ b/Result/profitability/1308.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM74"/>
+  <dimension ref="A1:AM75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -669,10 +669,10 @@
         <v>1.1</v>
       </c>
       <c r="M2" t="n">
-        <v>-0.21125</v>
+        <v>-0.16</v>
       </c>
       <c r="N2" t="n">
-        <v>5.70875</v>
+        <v>7.45</v>
       </c>
       <c r="O2" t="n">
         <v>1</v>
@@ -780,10 +780,10 @@
         <v>1.02</v>
       </c>
       <c r="M3" t="n">
-        <v>-0.03875000000000001</v>
+        <v>0.02625000000000001</v>
       </c>
       <c r="N3" t="n">
-        <v>8.0625</v>
+        <v>9.70875</v>
       </c>
       <c r="O3" t="n">
         <v>1</v>
@@ -899,10 +899,10 @@
         <v>0.34</v>
       </c>
       <c r="M4" t="n">
-        <v>0.0625</v>
+        <v>0.11875</v>
       </c>
       <c r="N4" t="n">
-        <v>9.505000000000001</v>
+        <v>10.485</v>
       </c>
       <c r="O4" t="n">
         <v>1</v>
@@ -1018,10 +1018,10 @@
         <v>-1.16</v>
       </c>
       <c r="M5" t="n">
-        <v>-0.03249999999999999</v>
+        <v>0.03625000000000003</v>
       </c>
       <c r="N5" t="n">
-        <v>5.883749999999999</v>
+        <v>7.256250000000001</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -1137,10 +1137,10 @@
         <v>0.76</v>
       </c>
       <c r="M6" t="n">
-        <v>0.125</v>
+        <v>0.16375</v>
       </c>
       <c r="N6" t="n">
-        <v>8.199999999999999</v>
+        <v>9.92625</v>
       </c>
       <c r="O6" t="n">
         <v>1</v>
@@ -1264,10 +1264,10 @@
         <v>1.18</v>
       </c>
       <c r="M7" t="n">
-        <v>0.305</v>
+        <v>0.38625</v>
       </c>
       <c r="N7" t="n">
-        <v>11.47125</v>
+        <v>12.46375</v>
       </c>
       <c r="O7" t="n">
         <v>1</v>
@@ -1391,10 +1391,10 @@
         <v>1.08</v>
       </c>
       <c r="M8" t="n">
-        <v>0.515</v>
+        <v>0.54625</v>
       </c>
       <c r="N8" t="n">
-        <v>13.35875</v>
+        <v>14.45875</v>
       </c>
       <c r="O8" t="n">
         <v>1</v>
@@ -9826,6 +9826,133 @@
       </c>
       <c r="AM74" t="n">
         <v>115.1</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>1308</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>115.2Q</t>
+        </is>
+      </c>
+      <c r="C75" t="n">
+        <v>1550</v>
+      </c>
+      <c r="D75" t="n">
+        <v>1326</v>
+      </c>
+      <c r="E75" t="n">
+        <v>224</v>
+      </c>
+      <c r="F75" t="n">
+        <v>14.46</v>
+      </c>
+      <c r="G75" t="n">
+        <v>168</v>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>10.83%</t>
+        </is>
+      </c>
+      <c r="I75" t="n">
+        <v>-121</v>
+      </c>
+      <c r="J75" t="n">
+        <v>47</v>
+      </c>
+      <c r="K75" t="n">
+        <v>30</v>
+      </c>
+      <c r="L75" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="M75" t="n">
+        <v>-0.3425</v>
+      </c>
+      <c r="N75" t="n">
+        <v>4.90125</v>
+      </c>
+      <c r="O75" t="n">
+        <v>1</v>
+      </c>
+      <c r="P75" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q75" t="n">
+        <v>1</v>
+      </c>
+      <c r="R75" t="n">
+        <v>1</v>
+      </c>
+      <c r="S75" t="n">
+        <v>1</v>
+      </c>
+      <c r="T75" t="n">
+        <v>1</v>
+      </c>
+      <c r="U75" t="n">
+        <v>0</v>
+      </c>
+      <c r="V75" t="n">
+        <v>115.2</v>
+      </c>
+      <c r="W75" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="X75" t="n">
+        <v>-1.25</v>
+      </c>
+      <c r="Y75" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="Z75" t="n">
+        <v>1.554770318021201</v>
+      </c>
+      <c r="AA75" t="n">
+        <v>0.55</v>
+      </c>
+      <c r="AB75" t="n">
+        <v>-1.1</v>
+      </c>
+      <c r="AC75" t="n">
+        <v>10.98</v>
+      </c>
+      <c r="AD75" t="n">
+        <v>3.155172413793104</v>
+      </c>
+      <c r="AE75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ75" t="inlineStr">
+        <is>
+          <t>EPS成長 / 毛利率成長</t>
+        </is>
+      </c>
+      <c r="AK75" t="n">
+        <v>115</v>
+      </c>
+      <c r="AL75" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM75" t="n">
+        <v>115.2</v>
       </c>
     </row>
   </sheetData>
